--- a/scrapers/resultado_mcdonalds.xlsx
+++ b/scrapers/resultado_mcdonalds.xlsx
@@ -467,7 +467,7 @@
       <c r="B2" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -511,7 +511,7 @@
       <c r="B3" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -555,7 +555,7 @@
       <c r="B4" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -595,7 +595,7 @@
       <c r="B5" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -635,7 +635,7 @@
       <c r="B6" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -679,7 +679,7 @@
       <c r="B7" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -719,7 +719,7 @@
       <c r="B8" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -763,7 +763,7 @@
       <c r="B9" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -803,7 +803,7 @@
       <c r="B10" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -843,7 +843,7 @@
       <c r="B11" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -883,7 +883,7 @@
       <c r="B12" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -927,7 +927,7 @@
       <c r="B13" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -971,7 +971,7 @@
       <c r="B14" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1015,7 +1015,7 @@
       <c r="B15" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1059,7 +1059,7 @@
       <c r="B16" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1103,7 +1103,7 @@
       <c r="B17" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1147,7 +1147,7 @@
       <c r="B18" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1191,7 +1191,7 @@
       <c r="B19" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1235,7 +1235,7 @@
       <c r="B20" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1275,7 +1275,7 @@
       <c r="B21" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1311,7 +1311,7 @@
       <c r="B22" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1347,7 +1347,7 @@
       <c r="B23" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1358,17 +1358,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>McTrío mediano Cuarto de Libra con Queso</t>
+          <t>Cajita Feliz Hamburguesa con Queso</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hamburguesa con carne de res, sazonada con una pizca de sal y pimienta con queso americano, cebolla, pepinillos, cátsup y mostaza.</t>
+          <t>Pide tu Cajita Feliz de Hamburguesa con Queso; Incluye papas kids y Yoplait</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>MX$169.00</t>
+          <t>MX$149.00</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
@@ -1383,7 +1383,7 @@
       <c r="B24" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1394,17 +1394,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>McTrío mediano BBQ Crispy Onion Doble</t>
+          <t>McTrío mediano McCrispy Spicy</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Hamburguesa con 2 Carnes Signature, salsa BBQ, cebolla caramelizada, queso cheddar blanco, csrispy onion, tocino y pan brioche.</t>
+          <t>McTrio Mediano McCrispy Spicy</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>MX$229.00</t>
+          <t>MX$159.00</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
@@ -1419,7 +1419,7 @@
       <c r="B25" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1430,17 +1430,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>McTrío Cuarto de Libra + Sundae Chocolate + Sobre Panini Coca</t>
+          <t>McTrío Hamb Dbl con Queso</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>McTrío Cuarto de Libra + Sundae Chocolate + Sobre Panini Coca</t>
+          <t>Hamburguesa con 2 carnes 100% de res, preparadas con cebolla, queso tipo americano, pepinillos, catsup y mostaza. Incluye papas medianas y refresco de 16Oz</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>MX$214.00</t>
+          <t>MX$105.00</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -1455,7 +1455,7 @@
       <c r="B26" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1466,17 +1466,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>McNuggets de Pollo 20 pzas</t>
+          <t>Cajita Feliz McNuggets de pollo 4 pzas</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>20 Nuggets de pechuga de pollo con una capa de empanizado doradito.</t>
+          <t>Pide tu Cajita Feliz de McNuggets 4 piezas; Incluye papas kids y Yoplait.</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>MX$199.00</t>
+          <t>MX$149.00</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
@@ -1491,7 +1491,7 @@
       <c r="B27" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>McTrio mediano McNuggets 10 pzas</t>
+          <t>McTrío mediano Cuarto de Libra con Queso</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>McTrío de 10 McNuggets, tiernos y jugosos trocitos 100% de pechuga de pollo con una capa de empanizado doradito. Incluye papas y refresco de 21oz.</t>
+          <t>Hamburguesa con carne de res, sazonada con una pizca de sal y pimienta con queso americano, cebolla, pepinillos, cátsup y mostaza.</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1527,7 +1527,7 @@
       <c r="B28" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1538,17 +1538,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Hamburguesa con Queso</t>
+          <t>McTrío Cuarto de Libra + Sundae Chocolate + Sobre Panini Coca</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hamburguesa con carne de res, queso tipo americano, pepinillos, cebolla, cátsup y mostaza</t>
+          <t>McTrío Cuarto de Libra + Sundae Chocolate + Sobre Panini Coca</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>MX$59.00</t>
+          <t>MX$214.00</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
@@ -1563,7 +1563,7 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1574,24 +1574,20 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>McTrío Plus</t>
+          <t>McTrío mediano McNifica</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>McTrío Hamburguesa con Queso + McFlurry Oreo</t>
+          <t>Hamburguesa con 1 carne de res, queso tipo americano, lechuga, cebolla, dos rebanadas de jitomate, mayonesa, cátsup, mostaza.</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>MX$139.00</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>MX$150.00</t>
-        </is>
-      </c>
+          <t>MX$169.00</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
@@ -1603,7 +1599,7 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1614,17 +1610,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>McNuggets de Pollo 4 pzas</t>
+          <t>McNuggets de Pollo 10 pzas</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>4 Nuggets de pechuga de pollo con una capa de empanizado doradito.</t>
+          <t>10 Nuggets de pechuga de pollo con una capa de empanizado doradito.</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>MX$59.00</t>
+          <t>MX$145.00</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
@@ -1639,7 +1635,7 @@
       <c r="B31" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1675,7 +1671,7 @@
       <c r="B32" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1711,7 +1707,7 @@
       <c r="B33" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1755,7 +1751,7 @@
       <c r="B34" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1799,7 +1795,7 @@
       <c r="B35" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1843,7 +1839,7 @@
       <c r="B36" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1887,7 +1883,7 @@
       <c r="B37" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1931,7 +1927,7 @@
       <c r="B38" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1967,7 +1963,7 @@
       <c r="B39" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2003,7 +1999,7 @@
       <c r="B40" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2039,7 +2035,7 @@
       <c r="B41" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2075,7 +2071,7 @@
       <c r="B42" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2111,7 +2107,7 @@
       <c r="B43" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2147,7 +2143,7 @@
       <c r="B44" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2183,7 +2179,7 @@
       <c r="B45" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2219,7 +2215,7 @@
       <c r="B46" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2259,7 +2255,7 @@
       <c r="B47" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2299,7 +2295,7 @@
       <c r="B48" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2343,7 +2339,7 @@
       <c r="B49" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2387,7 +2383,7 @@
       <c r="B50" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2431,7 +2427,7 @@
       <c r="B51" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2475,7 +2471,7 @@
       <c r="B52" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2519,7 +2515,7 @@
       <c r="B53" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2563,7 +2559,7 @@
       <c r="B54" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2607,7 +2603,7 @@
       <c r="B55" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2643,7 +2639,7 @@
       <c r="B56" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2679,7 +2675,7 @@
       <c r="B57" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2715,7 +2711,7 @@
       <c r="B58" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2751,7 +2747,7 @@
       <c r="B59" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2787,7 +2783,7 @@
       <c r="B60" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2827,7 +2823,7 @@
       <c r="B61" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2867,7 +2863,7 @@
       <c r="B62" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2907,7 +2903,7 @@
       <c r="B63" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2947,7 +2943,7 @@
       <c r="B64" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2983,7 +2979,7 @@
       <c r="B65" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3019,7 +3015,7 @@
       <c r="B66" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3055,7 +3051,7 @@
       <c r="B67" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3091,7 +3087,7 @@
       <c r="B68" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3127,7 +3123,7 @@
       <c r="B69" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3163,7 +3159,7 @@
       <c r="B70" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3199,7 +3195,7 @@
       <c r="B71" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3235,7 +3231,7 @@
       <c r="B72" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3271,7 +3267,7 @@
       <c r="B73" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3307,7 +3303,7 @@
       <c r="B74" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3347,7 +3343,7 @@
       <c r="B75" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3383,7 +3379,7 @@
       <c r="B76" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3419,7 +3415,7 @@
       <c r="B77" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3455,7 +3451,7 @@
       <c r="B78" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3491,7 +3487,7 @@
       <c r="B79" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3527,7 +3523,7 @@
       <c r="B80" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3563,7 +3559,7 @@
       <c r="B81" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3599,7 +3595,7 @@
       <c r="B82" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3635,7 +3631,7 @@
       <c r="B83" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3671,7 +3667,7 @@
       <c r="B84" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3707,7 +3703,7 @@
       <c r="B85" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3743,7 +3739,7 @@
       <c r="B86" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3779,7 +3775,7 @@
       <c r="B87" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3815,7 +3811,7 @@
       <c r="B88" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3851,7 +3847,7 @@
       <c r="B89" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3887,7 +3883,7 @@
       <c r="B90" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3923,7 +3919,7 @@
       <c r="B91" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3959,7 +3955,7 @@
       <c r="B92" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3995,7 +3991,7 @@
       <c r="B93" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -4031,7 +4027,7 @@
       <c r="B94" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -4067,7 +4063,7 @@
       <c r="B95" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -4103,7 +4099,7 @@
       <c r="B96" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -4139,7 +4135,7 @@
       <c r="B97" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -4175,7 +4171,7 @@
       <c r="B98" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -4211,7 +4207,7 @@
       <c r="B99" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -4247,7 +4243,7 @@
       <c r="B100" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -4283,7 +4279,7 @@
       <c r="B101" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -4319,7 +4315,7 @@
       <c r="B102" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -4355,7 +4351,7 @@
       <c r="B103" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4391,7 +4387,7 @@
       <c r="B104" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4427,7 +4423,7 @@
       <c r="B105" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4463,7 +4459,7 @@
       <c r="B106" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4499,7 +4495,7 @@
       <c r="B107" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4535,7 +4531,7 @@
       <c r="B108" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4571,7 +4567,7 @@
       <c r="B109" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4607,7 +4603,7 @@
       <c r="B110" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4643,7 +4639,7 @@
       <c r="B111" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4679,7 +4675,7 @@
       <c r="B112" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4715,7 +4711,7 @@
       <c r="B113" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4751,7 +4747,7 @@
       <c r="B114" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4787,7 +4783,7 @@
       <c r="B115" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4823,7 +4819,7 @@
       <c r="B116" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4859,7 +4855,7 @@
       <c r="B117" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4895,7 +4891,7 @@
       <c r="B118" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4931,7 +4927,7 @@
       <c r="B119" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4967,7 +4963,7 @@
       <c r="B120" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -5003,7 +4999,7 @@
       <c r="B121" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -5039,7 +5035,7 @@
       <c r="B122" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -5075,7 +5071,7 @@
       <c r="B123" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -5111,7 +5107,7 @@
       <c r="B124" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -5147,7 +5143,7 @@
       <c r="B125" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -5191,7 +5187,7 @@
       <c r="B126" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -5227,7 +5223,7 @@
       <c r="B127" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -5271,7 +5267,7 @@
       <c r="B128" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -5311,7 +5307,7 @@
       <c r="B129" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -5355,7 +5351,7 @@
       <c r="B130" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -5391,7 +5387,7 @@
       <c r="B131" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -5427,7 +5423,7 @@
       <c r="B132" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -5463,7 +5459,7 @@
       <c r="B133" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -5499,7 +5495,7 @@
       <c r="B134" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -5535,7 +5531,7 @@
       <c r="B135" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -5571,7 +5567,7 @@
       <c r="B136" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -5607,7 +5603,7 @@
       <c r="B137" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -5643,7 +5639,7 @@
       <c r="B138" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -5679,7 +5675,7 @@
       <c r="B139" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -5715,7 +5711,7 @@
       <c r="B140" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -5751,7 +5747,7 @@
       <c r="B141" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -5787,7 +5783,7 @@
       <c r="B142" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -5823,7 +5819,7 @@
       <c r="B143" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -5859,7 +5855,7 @@
       <c r="B144" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -5895,7 +5891,7 @@
       <c r="B145" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -5931,7 +5927,7 @@
       <c r="B146" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -5967,7 +5963,7 @@
       <c r="B147" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -6003,7 +5999,7 @@
       <c r="B148" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -6039,7 +6035,7 @@
       <c r="B149" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -6075,7 +6071,7 @@
       <c r="B150" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -6111,7 +6107,7 @@
       <c r="B151" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -6147,7 +6143,7 @@
       <c r="B152" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -6183,7 +6179,7 @@
       <c r="B153" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -6219,7 +6215,7 @@
       <c r="B154" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -6255,7 +6251,7 @@
       <c r="B155" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -6291,7 +6287,7 @@
       <c r="B156" t="inlineStr">
         <is>
           <t>DiDi Repartidor
-30 Min</t>
+35 Min</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
